--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table118.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table118.xlsx
@@ -310,7 +310,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,6 +350,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,14 +537,14 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="6" borderId="3" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2192,17 +2198,17 @@
       <c r="HE3" s="22"/>
     </row>
     <row r="4" spans="1:213" s="2" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
     </row>
     <row r="5" spans="1:213" s="3" customFormat="1" ht="11.25" customHeight="1">
       <c r="A5" s="11" t="s">
@@ -3000,7 +3006,7 @@
       <c r="N31" s="23"/>
     </row>
     <row r="32" spans="1:14" s="4" customFormat="1" ht="11">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="33" t="s">
         <v>40</v>
       </c>
       <c r="B32" s="32">
